--- a/xlsx/asset_import_template.xlsx
+++ b/xlsx/asset_import_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -34,13 +34,28 @@
     <t xml:space="preserve">quantity</t>
   </si>
   <si>
+    <t xml:space="preserve">СМЕННАЯ ПРЕСС-ФОРМУ ПОДСТАВКА НА ТРЕВЕРСЕГЛАВНОГО КАТАЛИЗАТОРА </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A01ZCHLHMJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RU01450099 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Производственный общий </t>
+  </si>
+  <si>
+    <t xml:space="preserve">080000009807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RU01000098 </t>
+  </si>
+  <si>
     <t xml:space="preserve">Сварочный цех</t>
   </si>
   <si>
-    <t xml:space="preserve">Производственный общий </t>
-  </si>
-  <si>
-    <t xml:space="preserve">080000009807</t>
+    <t xml:space="preserve">RU01050099 </t>
   </si>
 </sst>
 </file>
@@ -333,13 +348,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="19.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -356,37 +372,43 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>970000000041</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>1</v>
+      <c r="B2" s="3" t="n">
+        <v>70000001327</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>970000000041</v>
@@ -396,6 +418,9 @@
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
